--- a/unitydata/excel/suit.xlsx
+++ b/unitydata/excel/suit.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="combat_set" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <ns3:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -128,8 +129,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2">
+  <fonts count="4" ns2:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,11 +219,11 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -490,132 +491,741 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="50.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="3" max="3" width="24" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="1">
+      <c r="A1" t="str" s="0">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str" s="0">
+        <v>suit</v>
+      </c>
+      <c r="C1" t="str" s="0">
+        <v>name</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str" s="0">
+        <v>CS</v>
+      </c>
+      <c r="B2" t="str" s="0">
+        <v>CS</v>
+      </c>
+      <c r="C2" t="str" s="0">
+        <v>CS</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1">
+      <c r="A3" s="1" t="str">
+        <v>套装编号</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v>2/3/4件基础属性与技能</v>
+      </c>
+      <c r="C3" t="str" s="1">
+        <v>名称</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str" s="0">
+        <v>number</v>
+      </c>
+      <c r="B4" t="str" s="0">
+        <v>json</v>
+      </c>
+      <c r="C4" t="str" s="0">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>1</v>
+      </c>
+      <c r="B5" t="str" s="0">
+        <v>[[[1,25,1200]],[],[]]</v>
+      </c>
+      <c r="C5" t="str" s="0">
+        <v>牛金牛</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <v>[[[1,13,1000]],[],[]]</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <v>室火猪</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B7" s="1" t="str">
+        <v>[[[1,23,1000]],[],[]]</v>
+      </c>
+      <c r="C7" t="str" s="1">
+        <v>奎木狼</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <v>[[[1,28,1500]],[],[]]</v>
+      </c>
+      <c r="C8" t="str" s="1">
+        <v>觜火猴</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <v>[[[1,17,1000]],[],[]]</v>
+      </c>
+      <c r="C9" t="str" s="1">
+        <v>参水猿</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <v>[[[1,15,1000]],[],[]]</v>
+      </c>
+      <c r="C10" t="str" s="1">
+        <v>昴日鸡</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <v>[[[1,32,1000]],[],[]]</v>
+      </c>
+      <c r="C11" t="str" s="1">
+        <v>亢金龙</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="str">
+        <v>[[[1,26,800]],[],[]]</v>
+      </c>
+      <c r="C12" t="str" s="1">
+        <v>心月狐</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="str">
+        <v>[[],[],[]]</v>
+      </c>
+      <c r="C13" t="str" s="1">
+        <v>星日马</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="str">
+        <v>[[],[],[]]</v>
+      </c>
+      <c r="C14" t="str" s="1">
+        <v>鬼金羊</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing ns1:id="Rf4dc58c656cc4c5b"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" t="str" s="0">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str" s="0">
+        <v>suit_id</v>
+      </c>
+      <c r="C1" t="str" s="0">
+        <v>pieces</v>
+      </c>
+      <c r="D1" t="str" s="0">
+        <v>effect_group</v>
+      </c>
+      <c r="E1" t="str" s="0">
+        <v>value</v>
+      </c>
+      <c r="F1" t="str" s="0">
+        <v>enabled</v>
+      </c>
+      <c r="G1" t="str" s="0">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" t="str" s="0">
+        <v>CS</v>
+      </c>
+      <c r="B2" t="str" s="0">
+        <v>CS</v>
+      </c>
+      <c r="C2" t="str" s="0">
+        <v>CS</v>
+      </c>
+      <c r="D2" t="str" s="0">
+        <v>CS</v>
+      </c>
+      <c r="E2" t="str" s="0">
+        <v>CS</v>
+      </c>
+      <c r="F2" t="str" s="0">
+        <v>CS</v>
+      </c>
+      <c r="G2" t="str" s="0">
+        <v>CS</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" t="str" s="0">
+        <v>id</v>
+      </c>
+      <c r="B3" t="str" s="0">
+        <v>suit_id</v>
+      </c>
+      <c r="C3" t="str" s="0">
+        <v>pieces</v>
+      </c>
+      <c r="D3" t="str" s="0">
+        <v>effect_group</v>
+      </c>
+      <c r="E3" t="str" s="0">
+        <v>value</v>
+      </c>
+      <c r="F3" t="str" s="0">
+        <v>enabled</v>
+      </c>
+      <c r="G3" t="str" s="0">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" t="str" s="0">
+        <v>number</v>
+      </c>
+      <c r="B4" t="str" s="0">
+        <v>number</v>
+      </c>
+      <c r="C4" t="str" s="0">
+        <v>number</v>
+      </c>
+      <c r="D4" t="str" s="0">
+        <v>number</v>
+      </c>
+      <c r="E4" t="str" s="0">
+        <v>number</v>
+      </c>
+      <c r="F4" t="str" s="0">
+        <v>number</v>
+      </c>
+      <c r="G4" t="str" s="0">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <v>base_attributes</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>30014</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="1" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="B7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <v>base_attributes</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>30024</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="1" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="B9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <v>base_attributes</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>30034</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="1" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="B11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <v>base_attributes</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="B12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>30044</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="1" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <v>base_attributes</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="1" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+      <c r="B14" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>30054</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="1" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+      <c r="B15" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="str">
+        <v>base_attributes</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="1" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+      <c r="B16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>30064</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+      <c r="C17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="str">
+        <v>base_attributes</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>30074</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+      <c r="C19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <v>base_attributes</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>30084</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+      <c r="C21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>30092</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>30094</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>15</v>
+      <c r="C23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>30102</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>30104</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <v>complete</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>